--- a/switches_zabbix.xlsx
+++ b/switches_zabbix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H67"/>
+  <dimension ref="A3:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="3">
@@ -531,8 +531,16 @@
           <t>RG_PARANA</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HP 1920-24</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Proximo a equipe de projetos/sala de monitoramento</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,8 +571,16 @@
           <t>RG_PARANA</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HP 1920-24</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sala de servidores</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -595,8 +611,16 @@
           <t>RG_PARANA</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HP 1920-24</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sala de servidores</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -627,8 +651,16 @@
           <t>RG_PARANA</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-4</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CPD</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -659,8 +691,16 @@
           <t>RG_PARANA</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Utilizado para o projeto Force</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -691,8 +731,16 @@
           <t>RG_PARANA</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HP 2530-24</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Rack do Comercial</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -723,8 +771,16 @@
           <t>RG_PARANA</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3com 2420-24</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -755,8 +811,16 @@
           <t>RG_PARANA</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HP 2530-24</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sala de servidores</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -787,8 +851,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -819,8 +891,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -851,8 +931,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -883,8 +971,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -915,8 +1011,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -947,8 +1051,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -979,8 +1091,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1011,8 +1131,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1043,8 +1171,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1075,8 +1211,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1107,8 +1251,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1139,8 +1291,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1171,8 +1331,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1203,8 +1371,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1235,8 +1411,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1267,8 +1451,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1299,8 +1491,16 @@
           <t>RG_BH</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1331,8 +1531,16 @@
           <t>RG_MOTUS</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>HP 1910 24 PORTAS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1363,8 +1571,16 @@
           <t>RG_MOTUS</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>HP 1910 24 PORTAS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1395,8 +1611,16 @@
           <t>RG_MOTUS</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>HP 1910 24 PORTAS</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1427,8 +1651,16 @@
           <t>RG_MOTUS</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>HP 1920 24 PORTAS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1459,8 +1691,16 @@
           <t>RG_MOTUS</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>HP 1920 24 PORTAS</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1491,8 +1731,16 @@
           <t>RG_MOTUS</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>HP 1920 24 PORTAS</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1523,8 +1771,16 @@
           <t>RG_MOTUS</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>HP 1930 24 PORTAS</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1555,8 +1811,16 @@
           <t>RG_MOTUS</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>HP 1810 GEN 2 24 PORTAS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1587,8 +1851,16 @@
           <t>RG_MOTUS</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>HP 1930 24 PORTAS</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SALA MUNDI (POSTO DE TRABALHO)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1619,8 +1891,16 @@
           <t>RG_MOTUS</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>HP 1930 24 PORTAS</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1651,8 +1931,16 @@
           <t>RG_GOIAS</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1683,8 +1971,16 @@
           <t>RG_GOIAS</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1715,8 +2011,16 @@
           <t>RG_GOIAS</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1747,8 +2051,16 @@
           <t>RG_GOIAS</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ARUBA 1830-48</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1779,8 +2091,16 @@
           <t>RG_GOIAS</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ARUBA 1830-48</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1811,8 +2131,16 @@
           <t>RG_GOIAS</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-24</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1843,8 +2171,16 @@
           <t>RG_GOIAS</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ARUBA 1830-48</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1875,26 +2211,34 @@
           <t>RG_GOIAS</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ARUBA 1830-48</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>10782</v>
+        <v>10802</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>V028_REG_CAMPINAS BASE 2 - SWTGPSCAM02-01</t>
+          <t>V037_REG_AMAZONAS - SWTGPSAMZ-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>V028_REG_CAMPINAS BASE 2 - SWTGPSCAM02-01</t>
+          <t>V037_REG_AMAZONAS - SWTGPSAMZ-01</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10.119.2.20</t>
+          <t>10.192.0.20</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1904,29 +2248,37 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RG_CAMPINAS</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+          <t>RG_AMAZONAS</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>10802</v>
+        <v>10803</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>V037_REG_AMAZONAS - SWTGPSAMZ-01</t>
+          <t>V037_REG_AMAZONAS - SWTGPSAMZ-02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>V037_REG_AMAZONAS - SWTGPSAMZ-01</t>
+          <t>V037_REG_AMAZONAS - SWTGPSAMZ-02</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10.192.0.20</t>
+          <t>10.192.0.21</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1939,26 +2291,34 @@
           <t>RG_AMAZONAS</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>10803</v>
+        <v>10804</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>V037_REG_AMAZONAS - SWTGPSAMZ-02</t>
+          <t>V037_REG_AMAZONAS - SWTGPSAMZ-03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>V037_REG_AMAZONAS - SWTGPSAMZ-02</t>
+          <t>V037_REG_AMAZONAS - SWTGPSAMZ-03</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10.192.0.21</t>
+          <t>10.192.0.22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1971,58 +2331,74 @@
           <t>RG_AMAZONAS</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10804</v>
+        <v>10860</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>V037_REG_AMAZONAS - SWTGPSAMZ-03</t>
+          <t>V015_TRADE TALENTOS-1701-64</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>V037_REG_AMAZONAS - SWTGPSAMZ-03</t>
+          <t>V015_TRADE TALENTOS-1701-64</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10.192.0.22</t>
+          <t>10.111.24.23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Switches=</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RG_AMAZONAS</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+          <t>RG_TRADE_TALENTOS</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>10860</v>
+        <v>10863</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-1701-64</t>
+          <t>V015_TRADE TALENTOS-0402</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-1701-64</t>
+          <t>V015_TRADE TALENTOS-0402</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10.111.24.23</t>
+          <t>10.111.24.28</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2035,26 +2411,34 @@
           <t>RG_TRADE_TALENTOS</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10863</v>
+        <v>10864</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-0402</t>
+          <t>V015_TRADE TALENTOS-0401</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-0402</t>
+          <t>V015_TRADE TALENTOS-0401</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10.111.24.28</t>
+          <t>10.111.24.29</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2067,26 +2451,34 @@
           <t>RG_TRADE_TALENTOS</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>10864</v>
+        <v>10866</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-0401</t>
+          <t>V015_TRADE TALENTOS-INT-05-01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-0401</t>
+          <t>V015_TRADE TALENTOS-INT-05-01</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10.111.24.29</t>
+          <t>10.111.24.34</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2099,26 +2491,34 @@
           <t>RG_TRADE_TALENTOS</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>10866</v>
+        <v>10867</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-INT-05-01</t>
+          <t>V015_TRADE TALENTOS-DC-05-01</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-INT-05-01</t>
+          <t>V015_TRADE TALENTOS-DC-05-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10.111.24.34</t>
+          <t>10.111.24.32</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2131,26 +2531,34 @@
           <t>RG_TRADE_TALENTOS</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Aruba 2930R-48</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>10867</v>
+        <v>10868</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-DC-05-01</t>
+          <t>V015_TRADE TALENTOS-DC-05-02</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-DC-05-01</t>
+          <t>V015_TRADE TALENTOS-DC-05-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10.111.24.32</t>
+          <t>10.111.24.31</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2163,26 +2571,34 @@
           <t>RG_TRADE_TALENTOS</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>10868</v>
+        <v>10913</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-DC-05-02</t>
+          <t>V015_TRADE TALENTOS-INT-05-02</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-DC-05-02</t>
+          <t>V015_TRADE TALENTOS-INT-05-02</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10.111.24.31</t>
+          <t>10.111.24.33</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2195,26 +2611,34 @@
           <t>RG_TRADE_TALENTOS</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>10913</v>
+        <v>10914</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-INT-05-02</t>
+          <t>V015_TRADE TALENTOS-SWWAN</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-INT-05-02</t>
+          <t>V015_TRADE TALENTOS-SWWAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10.111.24.33</t>
+          <t>10.111.24.20</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2232,21 +2656,21 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>10914</v>
+        <v>10828</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-SWWAN</t>
+          <t>V015_TRADE TALENTOS-0101</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-SWWAN</t>
+          <t>V015_TRADE TALENTOS-0101</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10.111.24.20</t>
+          <t>10.111.24.24</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2259,36 +2683,44 @@
           <t>RG_TRADE_TALENTOS</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>10828</v>
+        <v>10829</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-0101</t>
+          <t>V018_REG_CEARA2-SWTGPSCEA2-01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>V015_TRADE TALENTOS-0101</t>
+          <t>V018_REG_CEARA2-SWTGPSCEA2-01</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10.111.24.24</t>
+          <t>10.185.4.22</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Switches=</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RG_TRADE_TALENTOS</t>
+          <t>RG_CEARA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -2296,53 +2728,61 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>10829</v>
+        <v>10875</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>V018_REG_CEARA2-SWTGPSCEA2-01</t>
+          <t>V044_REG_ARARAS - SWTGPSARA-01</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>V018_REG_CEARA2-SWTGPSCEA2-01</t>
+          <t>V044_REG_ARARAS - SWTGPSARA-01</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10.185.4.22</t>
+          <t>10.119.14.21</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Switch=</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RG_CEARA</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+          <t>RG_ARARAS</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10875</v>
+        <v>10876</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>V044_REG_ARARAS - SWTGPSARA-01</t>
+          <t>V044_REG_ARARAS - SWTGPSARA-02</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>V044_REG_ARARAS - SWTGPSARA-01</t>
+          <t>V044_REG_ARARAS - SWTGPSARA-02</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10.119.14.21</t>
+          <t>10.119.14.22</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2355,168 +2795,2956 @@
           <t>RG_ARARAS</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>10876</v>
-      </c>
+      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>V044_REG_ARARAS - SWTGPSARA-02</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>V044_REG_ARARAS - SWTGPSARA-02</t>
-        </is>
-      </c>
+          <t>V026_REG_CAMPINAS - SWTCMP-01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10.119.14.22</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Switch=</t>
-        </is>
-      </c>
+          <t>10.119.2.20</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RG_ARARAS</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+          <t>REG_CAMPINAS</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ARUBA 1830-48</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>10901</v>
-      </c>
+      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
+          <t>V026_REG_CAMPINAS - SWTCMP-02</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>10.119.0.21</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>REG_CAMPINAS</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>V026_REG_CAMPINAS - SWTCMP-03</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>10.119.0.22</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>REG_CAMPINAS</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>V026_REG_CAMPINAS - SWTCMP-04</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>10.119.0.23</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>REG_CAMPINAS</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>V026_REG_CAMPINAS - SWTCMP-05</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>10.119.0.24</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>REG_CAMPINAS</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>V026_REG_CAMPINAS - SWTCMP-06</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>10.119.0.25</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>REG_CAMPINAS</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>V026_REG_CAMPINAS - SWTCMP-07</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>10.119.0.26</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>REG_CAMPINAS</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>V026_REG_CAMPINAS - SWTCMP-08</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>10.119.0.27</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>REG_CAMPINAS</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>V026_REG_CAMPINAS - SWTCMP-09</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>10.119.0.28</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>REG_CAMPINAS</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>V026_REG_CAMPINAS - SWTCMP-10</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>10.119.0.29</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>REG_CAMPINAS</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>V015_TRADE TALENTOS-1501</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>10.111.24.21</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>RG_TRADE_TALENTOS</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>V015_TRADE TALENTOS-04-02</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>10.111.24.30</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>RG_TRADE_TALENTOS</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>V015_TRADE TALENTOS-0104</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>10.111.24.27</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>RG_TRADE_TALENTOS</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>V015_TRADE TALENTOS-0103</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>10.111.24.25</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>RG_TRADE_TALENTOS</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>V015_TRADE TALENTOS-0102</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>10.111.24.26</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>RG_TRADE_TALENTOS</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>V015_TRADE TALENTOS-66-P17</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>10.111.24.22</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>RG_TRADE_TALENTOS</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>V015_TRADETALENTOS_SWT01-CORE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>10.111.24.1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>RG_TRADE_TALENTOS</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>V018_REG_CEARA - SWTCEA-07</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>192.168.85.26</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>RG_CEARA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>HP1930</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>V018_REG_CEARA - SWTCEA-06</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>192.168.85.25</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>RG_CEARA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>HP1930</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>V018_REG_CEARA - SWTCEA-05</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>192.168.85.24</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>RG_CEARA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>HP1930</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>V018_REG_CEARA - SWTCEA-04</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>192.168.85.23</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>RG_CEARA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>HP1930</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>V018_REG_CEARA - SWTCEA-03</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>192.168.85.22</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>RG_CEARA</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>HP1930</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>V018_REG_CEARA - SWTCEA-02</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>192.168.85.21</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>RG_CEARA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>HP1930</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>V018_REG_CEARA - SWTCEA-01</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>192.168.85.20</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>RG_CEARA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>HP1930</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>V017_SWT_SWTGPSBR-02</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>10.161.0.21</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>RG_GLOBAL SEGURANCA</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>V017_SWT_SWTGPSBR-01</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>10.161.0.20</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>RG_GLOBAL SEGURANCA</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>V010_MOTUS-MATRIZ - SWTMOTUS-10</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>10.111.0.18</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>RG_MOTUS</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Salta de Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>V009_RUDDER_SWTRDD03</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>172.16.112.22</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>REG_RUDDER</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>V009_RUDDER_SWTRDD04</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>172.16.112.23</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>REG_RUDDER</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>V009_RUDDER_SWTRDD05</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>172.16.112.24</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>REG_RUDDER</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>V009_RUDDER_SWTRDD07</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>172.16.112.25</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>REG_RUDDER</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>V009_RUDDER_SWTRDD08</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>172.16.112.26</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>REG_RUDDER</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>V009_RUDDER_SWTRDD06</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>172.16.112.55</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>REG_RUDDER</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>V019_REGIONAL SAO LEOPOLDO - SWTRSL-04</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>192.168.52.24</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>REG_SAO LEOPOLDO</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>HP 1930-48</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>V019_REGIONAL SAO LEOPOLDO - SWTRSL-05</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>192.168.52.25</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>REG_SAO LEOPOLDO</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>HP 1930-48</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>V019_REGIONAL SAO LEOPOLDO - SWTRSL-07</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>192.168.52.28</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>REG_SAO LEOPOLDO</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>HP1930-48</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>V019_REGIONAL SAO LEOPOLDO - SWTRSL-08</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>192.168.52.30</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>REG_SAO LEOPOLDO</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>HP 1930-48</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>V021_REG_BAHIA - SWTBAH-01</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>10.171.0.20</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>REG_BAHIA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>V021_REG_BAHIA - SWTBAH-02</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>10.171.0.21</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>REG_BAHIA</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>V021_REG_BAHIA - SWTBAH-03</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>10.171.0.22</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>REG_BAHIA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>V021_REG_BAHIA - SWTBAH-04</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>10.171.0.23</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>REG_BAHIA</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>V021_REG_BAHIA - SWTBAH-05</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>10.171.0.24</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>REG_BAHIA</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>V021_REG_BAHIA - SWTBAH-06</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>10.171.0.25</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>REG_BAHIA</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>V022_LOGHIS- SWTLGHS-01</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>10.111.6.20</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>REG_LOGHIS</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>V027_REG_SOROCABA - SWTSOR-01</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>10.115.0.20</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>REG_SOROCABA</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>V032_REG_MARANHAO_SWTMAR - 02</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>10.198.0.21</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>REG_MARANHAO</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>V032_REG_MARANHAO_SWTMAR - 01</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>10.198.0.20</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>REG_MARANHAO</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>V025_REG_RJ-RJO-SW10</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>192.168.21.21</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>LEG_RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>HP 1920S-24</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>V025_REG_RJ - RJO-SW09</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>192.168.21.19</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>LEG_RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-24 PORTAS</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>V025_REG_RJ - RJO-SW08</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>192.168.21.18</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>LEG_RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-24</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>V025_REG_RJ - RJO-SW07</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>192.168.21.17</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>LEG_RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>V025_REG_RJ - RJO-SW06</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>192.168.21.16</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>LEG_RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>HP1820-24</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>V025_REG_RJ - RJO-SW05</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>192.168.21.15</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>LEG_RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>HP1910-24</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>V025_REG_RJ - RJO-SW04</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>192.168.21.14</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>LEG_RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>HP1905-24</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>V025_REG_RJ - RJO-SW03</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>192.168.21.13</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>LEG_RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>HP1905-24</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>V025_REG_RJ - RJO-SW02</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>192.168.21.12</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>LEG_RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>HP1910-24</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>V025_REG_RJ - RJO-SW01</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>192.168.21.11</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>LEG_RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>HP1910-24</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>V031_REG_ESPIRITO SANTO - SWTRES-03</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>10.127.0.22</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>REG_ESPIRITO SANTO</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>ARUBA 1930</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>V031_REG_ESPIRITO SANTO - SWTRES-02</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>10.127.0.21</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>REG_ESPIRITO SANTO</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>V031_REG_ESPIRITO SANTO - SWTRES-01</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>10.127.0.20</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>REG_ESPIRITO SANTO</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ABC - SWITCH - SWTABC-04</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>10.111.10.23</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>REG_ABC</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>ARUBA 1830 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ABC - SWITCH - SWTABC-03</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>10.111.10.22</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>REG_ABC</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>ARUBA 1830 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ABC - SWITCH - SWTABC-02</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>10.111.10.21</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>REG_ABC</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>ARUBA 1830 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>V020_REGIONAL SJC - SWTSJC-05</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>10.112.0.24</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>REG_SJC</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>V020_REGIONAL SJC - SWTSJC-04</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>10.112.0.23</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>REG_SJC</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>V020_REGIONAL SJC - SWTSJC-03</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>10.112.0.22</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>REG_SJC</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>ARUBA 1830-48</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>V020_REGIONAL SJC - SWTSJC-02</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>10.112.0.21</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>REG_SJC</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>V020_REGIONAL SJC - SWTSJC-01</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>10.112.0.20</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>REG_SJC</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>V030_REG_UBERLANDIA - SWTUBL-CORE</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>10.134.0.20</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>REG_UBERLANDIA</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48P</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>V030_REG_UBERLANDIA - SWTUBL-06</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>10.134.0.25</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>REG_UBERLANDIA</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>ARUBA 1830 48G</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>V030_REG_UBERLANDIA - SWTUBL-05</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>10.134.0.24</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>REG_UBERLANDIA</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>ARUBA 1830 48G</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>V030_REG_UBERLANDIA - SWTUBL-04</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>10.134.0.23</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>REG_UBERLANDIA</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>ARUBA 1830 48G</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>V030_REG_UBERLANDIA - SWTUBL-03</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>10.134.0.22</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>REG_UBERLANDIA</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>HP 1810-48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>V034_TLSV PORTO ALEGRE - SWT-TLSV04</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>10.152.0.23</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>REG_TLSV_POA</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>ARUBA 1830-48</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>V034_TLSV PORTO ALEGRE - SWT-TLSV02</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>10.152.0.21</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>REG_TLSV_POA</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>ARUBA 1830</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>V034_TLSV PORTO ALEGRE - SWT-TLSV01</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>10.152.0.20</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>REG_TLSV_POA</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>ARUBA 1830</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>V045_REGIONAL-PARA_SWITCH_01</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>10.191.0.20</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>REG_PARA</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48P</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>V043_REG_PERNAMBUCO - SWTGPSPE-01</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>V043_REG_PERNAMBUCO - SWTGPSPE-01</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
         <is>
           <t>10.181.0.20</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Switch=</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>RG_PERNANBUCO</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>10945</v>
-      </c>
-      <c r="B65" t="inlineStr">
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>RG_PERNAMBUCO</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>V049_REG_MACAE01 - SWTMAC_LC_03</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>10.121.4.22</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>REG_MACAE</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>V049_REG_MACAE01 - SWTMAC_LC_02</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>10.121.4.21</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>REG_MACAE</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>V049_REG_MACAE01 - SWTMAC_LC_01</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>10.121.4.20</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>REG_MACAE</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
         <is>
           <t>V037_REG_RIO GRANDE DO NORTE - SWTGPSRN-02</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>V037_REG_RIO GRANDE DO NORTE - SWTGPSRN-02</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
         <is>
           <t>10.184.0.21</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Nenhuma</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>RG_RIO_GRANDE_DO_NOIRTE</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>10929</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>V017_SWT_SWTGPSBR-01</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>V017_SWT_SWTGPSBR-01</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>10.161.0.20</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Nenhuma</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>RG_BR</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>10930</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>V017_SWT_SWTGPSBR-02</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>V017_SWT_SWTGPSBR-02</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>10.161.0.21</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Nenhuma</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>RG_BR</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>REG_RIO GRANDE DO NORTE</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ALAGOAS - SWITCH - SWTALG-01</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>10.182.0.20</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>REG_ALAGOAS</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ALAGOAS - SWITCH - SWTALG-02</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>10.182.0.21</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>REG_ALAGOAS</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>V053_REG_RHMED -SWTRHMED-01</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>10.121.8.20</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>REG_RHMED</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>V053_REG_RHMED -SWTRHMED-02</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>10.121.8.21</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>REG_RHMED</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>V053_REG_RHMED -SWTRHMED-03</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>10.121.8.22</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>REG_RHMED</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>V053_REG_RHMED -SWTRHMED-04</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>10.121.8.23</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>REG_RHMED</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>V053_REG_RHMED -SWTRHMED-05</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>10.121.8.24</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>REG_RHMED</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>ARUBA 1930-48</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>V053_REG_RHMED -SWTRHMED-06</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>10.121.8.25</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>REG_RHMED</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>V053_REG_RHMED -SWTRHMED-07</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>10.121.8.26</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>REG_RHMED</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>V053_REG_RHMED -SWTRHMED-08</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>10.121.8.27</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>REG_RHMED</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>V053_REG_RHMED -SWTRHMED-09</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>10.121.8.28</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>REG_RHMED</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>V053_REG_RHMED -SWTRHMED-10</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>10.121.8.29</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>REG_RHMED</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>V053_REG_RHMED -SWTRHMED-11</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>10.121.8.30</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>REG_RHMED</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CAXIAS DO SUL - SWITCH - SWITCH_02</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>10.154.0.21</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>REG_CAXIAS</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>NUTRICAR - SWITCH - SWTNUT-01</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>10.111.14.20</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>REG_NUTRICAR</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Não Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>NUTRICAR - SWITCH - SWTNUT-03</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>10.111.14.22</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>REG_NUTRICAR</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>ARUBA 1930 48 PORTAS</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Não informado</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
